--- a/Marketing Campaign Research Database.xlsx
+++ b/Marketing Campaign Research Database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,12 +912,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fff0b375-9b47-41cc-b417-49a4aec4c07c</t>
+          <t>c515e9cd-3266-46ef-9a3c-2c2629b70b0a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-16T11:03:36+00:00</t>
+          <t>2026-10-17T05:56:02+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -937,22 +937,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Recommendation from friends or family</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Buy-one-get-one offer</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -987,29 +987,29 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bd853548-a273-4ae2-838c-d1315b85f8bb</t>
+          <t>bb168994-a261-4285-9c68-b70de2b51906</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-16T12:58:08+00:00</t>
+          <t>2026-10-17T06:06:06+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18–22</t>
+          <t>Above 45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1019,22 +1019,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Other / I rarely purchase online</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1054,34 +1054,34 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Buy-one-get-one offer</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>c515e9cd-3266-46ef-9a3c-2c2629b70b0a</t>
+          <t>f43a9fb2-4892-417b-a29a-17be17ca9d1f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-17T05:56:02+00:00</t>
+          <t>2026-10-17T06:09:19+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1091,29 +1091,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Very often</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Other / I rarely purchase online</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>I see too many advertisements</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Buy-one-get-one offer</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1158,22 +1158,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bb168994-a261-4285-9c68-b70de2b51906</t>
+          <t>369cfc3a-930d-4786-b061-a9499455a895</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-17T06:06:06+00:00</t>
+          <t>2026-10-17T06:13:11+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Above 45</t>
+          <t>18–22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other / I rarely purchase online</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1193,42 +1193,42 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Price or discount</t>
+          <t>Recommendation from friends or family</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Buy-one-get-one offer</t>
+          <t>Coupon or promo code</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1240,12 +1240,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f43a9fb2-4892-417b-a29a-17be17ca9d1f</t>
+          <t>ecf15066-1933-4b3a-8eb9-3221d01638f6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-17T06:09:19+00:00</t>
+          <t>2026-10-17T06:13:47+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other / I rarely purchase online</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>369cfc3a-930d-4786-b061-a9499455a895</t>
+          <t>97dff2b2-8899-49a8-a287-79551ec1cf6a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-17T06:13:11+00:00</t>
+          <t>2026-10-17T06:15:02+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Google/Search</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1357,27 +1357,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Recommendation from friends or family</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>The price or offer is unattractive</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Coupon or promo code</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1404,12 +1404,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ecf15066-1933-4b3a-8eb9-3221d01638f6</t>
+          <t>8527afca-ee6c-4f39-8a78-c280af8f3c8d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-17T06:13:47+00:00</t>
+          <t>2026-10-17T06:27:29+00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Brand reputation</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1486,12 +1486,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>97dff2b2-8899-49a8-a287-79551ec1cf6a</t>
+          <t>c02bf9e6-ab59-4ca9-a1df-e25af9486f18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-17T06:15:02+00:00</t>
+          <t>2026-10-17T06:29:12+00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Very often</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1516,22 +1516,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>The price or offer is unattractive</t>
+          <t>The product is irrelevant to me</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Buy-one-get-one offer</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1568,12 +1568,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8527afca-ee6c-4f39-8a78-c280af8f3c8d</t>
+          <t>9204f951-17ad-4906-8464-8d184c63d414</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-17T06:27:29+00:00</t>
+          <t>2026-10-17T07:51:28+00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1598,32 +1598,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Brand reputation</t>
+          <t>The advertisement itself</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>The product is irrelevant to me</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Free delivery</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1650,12 +1650,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>c02bf9e6-ab59-4ca9-a1df-e25af9486f18</t>
+          <t>1462968c-4df5-4f38-88f4-fe2cf6851998</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-17T06:29:12+00:00</t>
+          <t>2026-10-17T10:16:18+00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1665,29 +1665,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1695,22 +1695,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Brand reputation</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1732,62 +1732,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9204f951-17ad-4906-8464-8d184c63d414</t>
+          <t>584ebf7b-ad73-47e9-87c4-54b9d2dc3a31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-17T07:51:28+00:00</t>
+          <t>2026-10-17T19:07:57+00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18–22</t>
+          <t>23–30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>The advertisement itself</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1814,37 +1814,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1462968c-4df5-4f38-88f4-fe2cf6851998</t>
+          <t>0493eb42-6292-4d55-8079-cc43729613b3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-17T10:16:18+00:00</t>
+          <t>2026-10-17T19:12:57+00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18–22</t>
+          <t>31–45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Very often</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Brand reputation</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Buy-one-get-one offer</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1896,32 +1896,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2e66c75d-a699-4d28-b7df-cbd04e009ed7</t>
+          <t>f6c2dbd1-3448-43ea-9e09-10d3a794f2c6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-17T18:54:59+00:00</t>
+          <t>2026-10-17T23:49:09+00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>31–45</t>
+          <t>Above 45</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Other / I rarely purchase online</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1941,22 +1941,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1966,29 +1966,29 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>584ebf7b-ad73-47e9-87c4-54b9d2dc3a31</t>
+          <t>99b44256-68aa-41ac-b9c5-369356bff5da</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-17T19:07:57+00:00</t>
+          <t>2026-10-18T05:09:00+00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23–30</t>
+          <t>31–45</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1998,32 +1998,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Cashback after purchase</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2060,17 +2060,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0493eb42-6292-4d55-8079-cc43729613b3</t>
+          <t>5e1b260a-2ae2-49d2-83ca-8f452c0bc3f0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-17T19:12:57+00:00</t>
+          <t>2026-10-18T05:36:21+00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>31–45</t>
+          <t>Under 18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Other / I rarely purchase online</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -2105,32 +2105,32 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>The advertisement itself</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>The product is irrelevant to me</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2142,62 +2142,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f6c2dbd1-3448-43ea-9e09-10d3a794f2c6</t>
+          <t>aef9d24e-9d0c-4302-855c-e70c6cee660c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-17T23:49:09+00:00</t>
+          <t>2026-10-18T10:16:14+00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Above 45</t>
+          <t>18–22</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Google/Search</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Other / I rarely purchase online</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I see too many advertisements</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2224,17 +2224,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>99b44256-68aa-41ac-b9c5-369356bff5da</t>
+          <t>f04f4893-fd8f-4a95-a551-29d2746862cf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-18T05:09:00+00:00</t>
+          <t>2026-10-18T12:28:14+00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>31–45</t>
+          <t>18–22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2244,47 +2244,47 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I see too many advertisements</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2306,27 +2306,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5e1b260a-2ae2-49d2-83ca-8f452c0bc3f0</t>
+          <t>b8a565c9-994e-4cf6-b911-3421aef9b97c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-18T05:36:21+00:00</t>
+          <t>2026-10-19T07:57:43+00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>Above 45</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>The advertisement itself</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Cashback after purchase</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2388,52 +2388,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aef9d24e-9d0c-4302-855c-e70c6cee660c</t>
+          <t>e06d0613-79bd-40e2-8ef0-89ea67ae0a89</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-18T10:16:14+00:00</t>
+          <t>2026-10-21T09:41:34+00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18–22</t>
+          <t>Above 45</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>I see too many advertisements</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2470,22 +2470,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>f04f4893-fd8f-4a95-a551-29d2746862cf</t>
+          <t>08a1034f-2303-490d-93f9-e826b8a3d7a6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-18T12:28:14+00:00</t>
+          <t>2026-10-21T09:55:55+00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18–22</t>
+          <t>31–45</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Google/Search</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>I see too many advertisements</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Cashback after purchase</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2552,32 +2552,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>b8a565c9-994e-4cf6-b911-3421aef9b97c</t>
+          <t>daf518c0-89db-4a9e-8a5b-6bb1b858a1a8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-19T07:57:43+00:00</t>
+          <t>2026-10-21T10:24:14+00:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Above 45</t>
+          <t>23–30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Other / I rarely purchase online</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Cashback after purchase</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2634,17 +2634,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>e06d0613-79bd-40e2-8ef0-89ea67ae0a89</t>
+          <t>902ab14b-6ea2-4fe0-818f-c8a236ff9da7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-21T09:41:34+00:00</t>
+          <t>2026-10-21T10:27:02+00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Above 45</t>
+          <t>Under 18</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2716,22 +2716,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08a1034f-2303-490d-93f9-e826b8a3d7a6</t>
+          <t>544c0530-6a56-4e22-8210-e4492be71d51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-21T09:55:55+00:00</t>
+          <t>2026-10-20T03:07:23+00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>31–45</t>
+          <t>Under 18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2741,42 +2741,42 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>The product is irrelevant to me</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2798,44 +2798,44 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>daf518c0-89db-4a9e-8a5b-6bb1b858a1a8</t>
+          <t>ffb5392a-6cf3-4c1c-9dfa-03147eb5c62b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-21T10:24:14+00:00</t>
+          <t>2026-10-17T13:21:26+00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>23–30</t>
+          <t>Under 18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -2843,32 +2843,32 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>The advertisement itself</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>I see too many advertisements</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2880,12 +2880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>902ab14b-6ea2-4fe0-818f-c8a236ff9da7</t>
+          <t>aefba00f-ffa3-4d64-91c8-4f2cbf3efe97</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-21T10:27:02+00:00</t>
+          <t>2026-10-16T20:42:33+00:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2895,29 +2895,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Other / I rarely purchase online</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -2925,17 +2925,17 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Recommendation from friends or family</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>I see too many advertisements</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Coupon or promo code</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2962,12 +2962,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>544c0530-6a56-4e22-8210-e4492be71d51</t>
+          <t>dcc41750-23a1-46cf-8c51-59edac35dc58</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20T03:07:23+00:00</t>
+          <t>2026-10-18T16:25:25+00:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2982,27 +2982,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Other / I rarely purchase online</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ffb5392a-6cf3-4c1c-9dfa-03147eb5c62b</t>
+          <t>22829758-9e77-4f20-87b8-4b4c4f08de3c</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-17T13:21:26+00:00</t>
+          <t>2026-10-20T01:22:42+00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3059,17 +3059,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Beauty and personal care</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3094,27 +3094,27 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>The advertisement itself</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>I see too many advertisements</t>
+          <t>The price or offer is unattractive</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3126,12 +3126,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>aefba00f-ffa3-4d64-91c8-4f2cbf3efe97</t>
+          <t>14905293-b3c0-4640-83ab-38f927b384c7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-16T20:42:33+00:00</t>
+          <t>2026-10-16T21:29:49+00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3151,22 +3151,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Other / I rarely purchase online</t>
+          <t>Beauty and personal care</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3181,22 +3181,22 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>I see too many advertisements</t>
+          <t>The price or offer is unattractive</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Coupon or promo code</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3208,17 +3208,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dcc41750-23a1-46cf-8c51-59edac35dc58</t>
+          <t>7dd8c3d7-55eb-4a9a-8d4e-dd8fbab2e051</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-18T16:25:25+00:00</t>
+          <t>2026-10-17T00:18:54+00:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>18–22</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3228,17 +3228,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Other / I rarely purchase online</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I see too many advertisements</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3290,17 +3290,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>22829758-9e77-4f20-87b8-4b4c4f08de3c</t>
+          <t>c93fe90f-14aa-4dbe-82eb-fe6d1fb8e714</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20T01:22:42+00:00</t>
+          <t>2026-10-16T14:34:26+00:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>18–22</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Very often</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Beauty and personal care</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3325,42 +3325,42 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Price or discount</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>The price or offer is unattractive</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Cashback after purchase</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Free delivery</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3372,22 +3372,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14905293-b3c0-4640-83ab-38f927b384c7</t>
+          <t>e7ff5aac-9648-4c76-bcbc-40198bfdbea8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-16T21:29:49+00:00</t>
+          <t>2026-10-21T11:29:24+00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Under 18</t>
+          <t>18–22</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Beauty and personal care</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Recommendation from friends or family</t>
+          <t>Price or discount</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>The price or offer is unattractive</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3454,12 +3454,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7dd8c3d7-55eb-4a9a-8d4e-dd8fbab2e051</t>
+          <t>3256610e-c690-4bdc-b178-109055c06a70</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-17T00:18:54+00:00</t>
+          <t>2026-10-18T14:51:33+00:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Very often</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3499,22 +3499,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>I see too many advertisements</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3536,12 +3536,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>c93fe90f-14aa-4dbe-82eb-fe6d1fb8e714</t>
+          <t>1d6a2c6d-ef86-47ae-b35d-5ae7026c04b1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-16T14:34:26+00:00</t>
+          <t>2026-10-19T20:39:29+00:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3561,27 +3561,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>The product is irrelevant to me</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Cashback after purchase</t>
+          <t>Coupon or promo code</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3618,12 +3618,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>e7ff5aac-9648-4c76-bcbc-40198bfdbea8</t>
+          <t>08c6d687-877c-4d39-94ec-dd66e50d4d0e</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-21T11:29:24+00:00</t>
+          <t>2026-10-19T15:59:30+00:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3633,17 +3633,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Google/Search</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3668,22 +3668,22 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Price or discount</t>
+          <t>The advertisement itself</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Buy-one-get-one offer</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3700,12 +3700,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3256610e-c690-4bdc-b178-109055c06a70</t>
+          <t>e4d1c987-d597-481e-acf0-d6a91569f899</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-18T14:51:33+00:00</t>
+          <t>2026-10-17T21:39:48+00:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1d6a2c6d-ef86-47ae-b35d-5ae7026c04b1</t>
+          <t>8552ad88-e15b-4260-8699-eca64416451d</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-19T20:39:29+00:00</t>
+          <t>2026-10-17T03:42:27+00:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3807,47 +3807,47 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Price or discount</t>
+          <t>Recommendation from friends or family</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Coupon or promo code</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3864,42 +3864,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08c6d687-877c-4d39-94ec-dd66e50d4d0e</t>
+          <t>9c1290c4-2694-4cb7-8cde-257830e6e64c</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-19T15:59:30+00:00</t>
+          <t>2026-10-16T09:36:35+00:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18–22</t>
+          <t>23–30</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Very often</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Beauty and personal care</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3914,27 +3914,27 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>The advertisement itself</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>The product is irrelevant to me</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Buy-one-get-one offer</t>
+          <t>Cashback after purchase</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3946,27 +3946,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>e4d1c987-d597-481e-acf0-d6a91569f899</t>
+          <t>77e3d2cf-4842-41f3-9951-14e60f50f7c8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-17T21:39:48+00:00</t>
+          <t>2026-10-20T22:37:25+00:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>18–22</t>
+          <t>23–30</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3976,14 +3976,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -3991,32 +3991,32 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Price or discount</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Free delivery</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4028,17 +4028,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8552ad88-e15b-4260-8699-eca64416451d</t>
+          <t>bf93c304-5780-4b42-a41b-90b1c88a5f85</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-17T03:42:27+00:00</t>
+          <t>2026-10-21T03:27:23+00:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>18–22</t>
+          <t>23–30</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4048,42 +4048,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Beauty and personal care</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Recommendation from friends or family</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4110,12 +4110,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9c1290c4-2694-4cb7-8cde-257830e6e64c</t>
+          <t>84799f98-8811-49f2-ae1b-845f708dae0b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-16T09:36:35+00:00</t>
+          <t>2026-10-19T13:47:56+00:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4125,17 +4125,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Beauty and personal care</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4155,32 +4155,32 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Cashback after purchase</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4192,12 +4192,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>77e3d2cf-4842-41f3-9951-14e60f50f7c8</t>
+          <t>3a99bf3b-de45-4452-9bd6-1fd0404bab8a</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20T22:37:25+00:00</t>
+          <t>2026-10-16T12:43:49+00:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4237,32 +4237,32 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Price or discount</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4274,12 +4274,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bf93c304-5780-4b42-a41b-90b1c88a5f85</t>
+          <t>b3dffb0f-80dd-4622-9c50-53d3e6f8db46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-21T03:27:23+00:00</t>
+          <t>2026-10-17T01:25:08+00:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Google/Search</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Beauty and personal care</t>
+          <t>Other / I rarely purchase online</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4309,42 +4309,42 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Free delivery</t>
+          <t>Buy-one-get-one offer</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4356,12 +4356,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>84799f98-8811-49f2-ae1b-845f708dae0b</t>
+          <t>c27dabb1-ea92-474e-b225-379a6796ef70</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-19T13:47:56+00:00</t>
+          <t>2026-10-17T16:09:02+00:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4371,47 +4371,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Food and groceries</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Sometimes</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Price or discount</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>The price or offer is unattractive</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Free delivery</t>
+          <t>Cashback after purchase</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4438,12 +4438,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3a99bf3b-de45-4452-9bd6-1fd0404bab8a</t>
+          <t>da27b61b-beef-4ca9-a325-d3e1051fdb75</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-16T12:43:49+00:00</t>
+          <t>2026-10-21T07:42:42+00:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4453,32 +4453,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4488,27 +4488,27 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Price or discount</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Cashback after purchase</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4520,12 +4520,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>b3dffb0f-80dd-4622-9c50-53d3e6f8db46</t>
+          <t>fd39725f-255d-4e23-8cf8-541685e9ff31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-17T01:25:08+00:00</t>
+          <t>2026-10-18T05:40:27+00:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Other / I rarely purchase online</t>
+          <t>Beauty and personal care</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Not sure</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -4570,27 +4570,27 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>The product is irrelevant to me</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Buy-one-get-one offer</t>
+          <t>Coupon or promo code</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4602,12 +4602,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>c27dabb1-ea92-474e-b225-379a6796ef70</t>
+          <t>4c50cf74-51ef-4b62-a355-ea1de2b21eb9</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-17T16:09:02+00:00</t>
+          <t>2026-10-19T16:08:02+00:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4637,32 +4637,32 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Price or discount</t>
+          <t>Brand reputation</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>The price or offer is unattractive</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4684,12 +4684,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>da27b61b-beef-4ca9-a325-d3e1051fdb75</t>
+          <t>b0ca7161-23d6-4b6d-a1fb-29df4b59a9ce</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-21T07:42:42+00:00</t>
+          <t>2026-10-19T21:26:28+00:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Google/Search</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4714,17 +4714,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -4766,12 +4766,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fd39725f-255d-4e23-8cf8-541685e9ff31</t>
+          <t>e4d5d02d-e7fe-4496-a3b4-ba5b0428c48b</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-18T05:40:27+00:00</t>
+          <t>2026-10-18T21:26:06+00:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Beauty and personal care</t>
+          <t>Clothing and fashion</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4811,32 +4811,32 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Coupon or promo code</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -4848,12 +4848,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4c50cf74-51ef-4b62-a355-ea1de2b21eb9</t>
+          <t>fefb4180-9c9c-4395-88ef-7aaf641db996</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-19T16:08:02+00:00</t>
+          <t>2026-10-17T17:09:00+00:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Beauty and personal care</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4893,17 +4893,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Brand reputation</t>
+          <t>Recommendation from friends or family</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>The product is irrelevant to me</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Cashback after purchase</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4930,12 +4930,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>b0ca7161-23d6-4b6d-a1fb-29df4b59a9ce</t>
+          <t>403d1af2-6fb2-4d88-8b14-7f912b9de368</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-19T21:26:28+00:00</t>
+          <t>2026-10-16T23:24:41+00:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Very often</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Beauty and personal care</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Price or discount</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4990,17 +4990,17 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Cashback after purchase</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>e4d5d02d-e7fe-4496-a3b4-ba5b0428c48b</t>
+          <t>743c05ff-96b6-4047-b779-57128b6e253c</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-18T21:26:06+00:00</t>
+          <t>2026-10-16T20:56:25+00:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5037,27 +5037,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Clothing and fashion</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Not sure</t>
-        </is>
-      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5072,17 +5072,17 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Free delivery</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5094,12 +5094,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fefb4180-9c9c-4395-88ef-7aaf641db996</t>
+          <t>749de868-e34c-4654-a6dc-870b89cc2d16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-17T17:09:00+00:00</t>
+          <t>2026-10-18T22:28:33+00:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Beauty and personal care</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5129,17 +5129,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Cannot remember</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5149,17 +5149,17 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Free delivery</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5176,12 +5176,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>403d1af2-6fb2-4d88-8b14-7f912b9de368</t>
+          <t>873fa18d-72b7-4443-86c9-4baef7c83996</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-16T23:24:41+00:00</t>
+          <t>2026-10-17T20:31:42+00:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Brand reputation</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5241,12 +5241,12 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>743c05ff-96b6-4047-b779-57128b6e253c</t>
+          <t>c959c23f-e9fc-4cd5-a40a-50db35d0e604</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-16T20:56:25+00:00</t>
+          <t>2026-10-16T11:48:18+00:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5313,17 +5313,17 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>The product is irrelevant to me</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5340,12 +5340,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>749de868-e34c-4654-a6dc-870b89cc2d16</t>
+          <t>e2e8ca74-d98c-46e0-8b7a-40d04e23856d</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-18T22:28:33+00:00</t>
+          <t>2026-10-21T10:54:59+00:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5375,27 +5375,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Cannot remember</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Recommendation from friends or family</t>
+          <t>Price or discount</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>The product is irrelevant to me</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5422,52 +5422,52 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>873fa18d-72b7-4443-86c9-4baef7c83996</t>
+          <t>3c057273-9038-4411-b3bc-b90d6635dede</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-17T20:31:42+00:00</t>
+          <t>2026-10-19T13:59:09+00:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>23–30</t>
+          <t>31–45</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Home and lifestyle</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
           <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Beauty and personal care</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5477,22 +5477,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Cashback after purchase</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -5504,32 +5504,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>c959c23f-e9fc-4cd5-a40a-50db35d0e604</t>
+          <t>59d2aa2f-3b2e-48f2-83a7-66216147a092</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-16T11:48:18+00:00</t>
+          <t>2026-10-18T13:51:49+00:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>23–30</t>
+          <t>31–45</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5554,22 +5554,22 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Free delivery</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5586,22 +5586,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>e2e8ca74-d98c-46e0-8b7a-40d04e23856d</t>
+          <t>30b96da3-f5d7-4546-8584-6b03328405ca</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-21T10:54:59+00:00</t>
+          <t>2026-10-20T11:34:50+00:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>23–30</t>
+          <t>31–45</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Price or discount</t>
+          <t>The advertisement itself</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>The product is irrelevant to me</t>
+          <t>The price or offer is unattractive</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5668,12 +5668,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3c057273-9038-4411-b3bc-b90d6635dede</t>
+          <t>6fe55d6d-e7a4-4652-9c75-cc308831023f</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-19T13:59:09+00:00</t>
+          <t>2026-10-21T12:50:19+00:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5693,22 +5693,22 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>Not sure</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5718,22 +5718,22 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Brand reputation</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Cashback after purchase</t>
+          <t>Buy-one-get-one offer</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5750,12 +5750,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>59d2aa2f-3b2e-48f2-83a7-66216147a092</t>
+          <t>bdeebebf-89f7-4147-bb61-911aedf9e96e</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-18T13:51:49+00:00</t>
+          <t>2026-10-16T20:20:12+00:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5765,17 +5765,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5790,22 +5790,22 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Price or discount</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -5832,12 +5832,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>30b96da3-f5d7-4546-8584-6b03328405ca</t>
+          <t>d9073e6f-47f8-40d8-93b9-cd2c09ac0bca</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-20T11:34:50+00:00</t>
+          <t>2026-10-20T07:06:56+00:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5882,27 +5882,27 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>The advertisement itself</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>The price or offer is unattractive</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Immediate price discount</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Free delivery</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -5914,12 +5914,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6fe55d6d-e7a4-4652-9c75-cc308831023f</t>
+          <t>d796284d-cb85-4051-8272-ab35b141a39b</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-21T12:50:19+00:00</t>
+          <t>2026-10-20T09:52:36+00:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5929,22 +5929,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Very often</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5959,17 +5959,17 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Brand reputation</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Buy-one-get-one offer</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5996,12 +5996,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bdeebebf-89f7-4147-bb61-911aedf9e96e</t>
+          <t>a897fddf-6f36-4b6d-94cc-6a4f9c0851da</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-16T20:20:12+00:00</t>
+          <t>2026-10-17T01:08:17+00:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6011,17 +6011,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6036,27 +6036,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Price or discount</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6078,12 +6078,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>d9073e6f-47f8-40d8-93b9-cd2c09ac0bca</t>
+          <t>dc15ef4a-f134-461f-a298-901007984cae</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-20T07:06:56+00:00</t>
+          <t>2026-10-21T09:10:13+00:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6108,17 +6108,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Google/Search</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Brand reputation</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6160,12 +6160,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>d796284d-cb85-4051-8272-ab35b141a39b</t>
+          <t>25f65856-0cfd-431f-a79b-e75d88016b31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-20T09:52:36+00:00</t>
+          <t>2026-10-18T17:27:44+00:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6175,62 +6175,62 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Product quality and features</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>I do not trust the advertisement</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Brand reputation</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>I do not trust the advertisement</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6242,12 +6242,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>a897fddf-6f36-4b6d-94cc-6a4f9c0851da</t>
+          <t>369804e0-ffb8-4dca-898a-4d029924048a</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-17T01:08:17+00:00</t>
+          <t>2026-10-17T16:23:11+00:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6272,47 +6272,47 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Google/Search</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Immediate price discount</t>
+          <t>Buy-one-get-one offer</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -6324,12 +6324,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dc15ef4a-f134-461f-a298-901007984cae</t>
+          <t>bb2ddf0d-9f47-4361-b14a-3067d2f87dc9</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-21T09:10:13+00:00</t>
+          <t>2026-10-17T13:27:00+00:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Brand reputation</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -6406,12 +6406,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25f65856-0cfd-431f-a79b-e75d88016b31</t>
+          <t>230ce8a2-9370-40a1-8b30-a2aa6c2236db</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-18T17:27:44+00:00</t>
+          <t>2026-10-20T23:18:24+00:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6421,52 +6421,52 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Food and groceries</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>The advertisement itself</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -6488,32 +6488,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>369804e0-ffb8-4dca-898a-4d029924048a</t>
+          <t>8e39762b-b862-408d-8502-aba46ab023f0</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-17T16:23:11+00:00</t>
+          <t>2026-10-20T13:42:53+00:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>31–45</t>
+          <t>Above 45</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Very often</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Beauty and personal care</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6533,27 +6533,27 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Product quality and features</t>
+          <t>Brand reputation</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>I do not trust the advertisement</t>
+          <t>I prefer researching products independently</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Buy-one-get-one offer</t>
+          <t>Free delivery</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6570,44 +6570,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>bb2ddf0d-9f47-4361-b14a-3067d2f87dc9</t>
+          <t>f59b2607-a6e7-46ba-b490-4d518c4f33c8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-17T13:27:00+00:00</t>
+          <t>2026-10-19T03:04:12+00:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>31–45</t>
+          <t>Above 45</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -6615,17 +6615,17 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>I see too many advertisements</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Free delivery</t>
+          <t>Cashback after purchase</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6652,32 +6652,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>230ce8a2-9370-40a1-8b30-a2aa6c2236db</t>
+          <t>a11eb8b3-501d-4ee8-9054-39ff57433e6b</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-20T23:18:24+00:00</t>
+          <t>2026-10-17T14:39:28+00:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>31–45</t>
+          <t>Above 45</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Google/Search</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Food and groceries</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6687,22 +6687,22 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>The advertisement itself</t>
+          <t>Customer reviews and ratings</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -6734,12 +6734,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8e39762b-b862-408d-8502-aba46ab023f0</t>
+          <t>5571a61f-fbab-4aea-a84a-3aabbf728603</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-20T13:42:53+00:00</t>
+          <t>2026-10-17T02:39:43+00:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Google/Search</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Beauty and personal care</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6779,27 +6779,27 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Brand reputation</t>
+          <t>Product quality and features</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Free delivery</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6816,22 +6816,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>f59b2607-a6e7-46ba-b490-4d518c4f33c8</t>
+          <t>98b02370-411a-496d-aac7-cd92709d3525</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-19T03:04:12+00:00</t>
+          <t>2026-10-16T09:59:53+00:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Above 45</t>
+          <t>23–30</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -6871,22 +6871,22 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>I see too many advertisements</t>
+          <t>I do not trust the advertisement</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Cashback after purchase</t>
+          <t>Immediate price discount</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -6898,77 +6898,77 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>a11eb8b3-501d-4ee8-9054-39ff57433e6b</t>
+          <t>a7406ce0-ccae-4cbe-8ca4-447f377ca12f</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-17T14:39:28+00:00</t>
+          <t>2026-10-17T13:10:22+00:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Above 45</t>
+          <t>23–30</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Home and lifestyle</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Customer reviews and ratings</t>
+          <t>Brand reputation</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>I prefer researching products independently</t>
+          <t>The price or offer is unattractive</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Free delivery</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -6980,52 +6980,52 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5571a61f-fbab-4aea-a84a-3aabbf728603</t>
+          <t>7fc26476-940c-4b2b-9eb3-f601a01ae572</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-17T02:39:43+00:00</t>
+          <t>2026-10-17T19:52:01+00:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Above 45</t>
+          <t>23–30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Google/Search</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Home and lifestyle</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7040,266 +7040,20 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Buy-one-get-one offer</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>98b02370-411a-496d-aac7-cd92709d3525</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-10-16T09:59:53+00:00</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>23–30</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Home and lifestyle</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Customer reviews and ratings</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>I do not trust the advertisement</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Immediate price discount</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>a7406ce0-ccae-4cbe-8ca4-447f377ca12f</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-10-17T13:10:22+00:00</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>23–30</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Google/Search</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Often</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Brand reputation</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>The price or offer is unattractive</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>None of these</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>7fc26476-940c-4b2b-9eb3-f601a01ae572</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-10-17T19:52:01+00:00</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>23–30</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Google/Search</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Home and lifestyle</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>E-commerce apps (Amazon, Flipkart, etc.)</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Product quality and features</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>I do not trust the advertisement</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>Buy-one-get-one offer</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>

--- a/Marketing Campaign Research Database.xlsx
+++ b/Marketing Campaign Research Database.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,7 +7335,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>d7db3732-da9c-4d59-a148-dd55ff9a16b0</t>
+          <t>cf305560-89a2-4d19-bd4c-67f25d911da7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7355,24 +7355,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-16T10:32:45+00:00</t>
+          <t>2026-10-16T10:31:49+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>d7db3732-da9c-4d59-a148-dd55ff9a16b0</t>
+          <t>cf305560-89a2-4d19-bd4c-67f25d911da7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -7402,14 +7402,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-16T10:33:11+00:00</t>
+          <t>2026-10-16T10:32:16+00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>d7db3732-da9c-4d59-a148-dd55ff9a16b0</t>
+          <t>cf305560-89a2-4d19-bd4c-67f25d911da7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7424,29 +7424,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-16T10:33:43+00:00</t>
+          <t>2026-10-16T10:33:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cf305560-89a2-4d19-bd4c-67f25d911da7</t>
+          <t>8fd8f966-95b4-4299-9c93-440b7e23caea</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7456,34 +7456,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-16T10:31:49+00:00</t>
+          <t>2026-10-16T10:49:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cf305560-89a2-4d19-bd4c-67f25d911da7</t>
+          <t>8fd8f966-95b4-4299-9c93-440b7e23caea</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7493,17 +7493,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7513,14 +7513,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-16T10:32:16+00:00</t>
+          <t>2026-10-16T10:50:18+00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cf305560-89a2-4d19-bd4c-67f25d911da7</t>
+          <t>8fd8f966-95b4-4299-9c93-440b7e23caea</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7530,17 +7530,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -7550,14 +7550,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-16T10:33:44+00:00</t>
+          <t>2026-10-16T10:50:24+00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8fd8f966-95b4-4299-9c93-440b7e23caea</t>
+          <t>c515e9cd-3266-46ef-9a3c-2c2629b70b0a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7567,34 +7567,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-16T10:49:55+00:00</t>
+          <t>2026-10-17T05:56:46+00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8fd8f966-95b4-4299-9c93-440b7e23caea</t>
+          <t>c515e9cd-3266-46ef-9a3c-2c2629b70b0a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7614,24 +7614,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-16T10:50:18+00:00</t>
+          <t>2026-10-17T05:57:21+00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8fd8f966-95b4-4299-9c93-440b7e23caea</t>
+          <t>c515e9cd-3266-46ef-9a3c-2c2629b70b0a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7656,19 +7656,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-16T10:50:24+00:00</t>
+          <t>2026-10-17T05:57:38+00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>c515e9cd-3266-46ef-9a3c-2c2629b70b0a</t>
+          <t>bb168994-a261-4285-9c68-b70de2b51906</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7683,29 +7683,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-17T05:56:46+00:00</t>
+          <t>2026-10-17T06:06:15+00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>c515e9cd-3266-46ef-9a3c-2c2629b70b0a</t>
+          <t>bb168994-a261-4285-9c68-b70de2b51906</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7735,14 +7735,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-17T05:57:21+00:00</t>
+          <t>2026-10-17T06:06:20+00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>c515e9cd-3266-46ef-9a3c-2c2629b70b0a</t>
+          <t>bb168994-a261-4285-9c68-b70de2b51906</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7757,29 +7757,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-17T05:57:38+00:00</t>
+          <t>2026-10-17T06:06:23+00:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bb168994-a261-4285-9c68-b70de2b51906</t>
+          <t>f43a9fb2-4892-417b-a29a-17be17ca9d1f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7789,17 +7789,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -7809,14 +7809,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-17T06:06:15+00:00</t>
+          <t>2026-10-17T06:09:36+00:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bb168994-a261-4285-9c68-b70de2b51906</t>
+          <t>f43a9fb2-4892-417b-a29a-17be17ca9d1f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7826,34 +7826,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-17T06:06:20+00:00</t>
+          <t>2026-10-17T06:09:46+00:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bb168994-a261-4285-9c68-b70de2b51906</t>
+          <t>f43a9fb2-4892-417b-a29a-17be17ca9d1f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7868,29 +7868,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-17T06:06:23+00:00</t>
+          <t>2026-10-17T06:09:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>f43a9fb2-4892-417b-a29a-17be17ca9d1f</t>
+          <t>ecf15066-1933-4b3a-8eb9-3221d01638f6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -7915,19 +7915,19 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-17T06:09:36+00:00</t>
+          <t>2026-10-17T06:14:01+00:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f43a9fb2-4892-417b-a29a-17be17ca9d1f</t>
+          <t>ecf15066-1933-4b3a-8eb9-3221d01638f6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7937,34 +7937,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-17T06:09:46+00:00</t>
+          <t>2026-10-17T06:14:03+00:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>f43a9fb2-4892-417b-a29a-17be17ca9d1f</t>
+          <t>ecf15066-1933-4b3a-8eb9-3221d01638f6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7974,34 +7974,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-17T06:09:55+00:00</t>
+          <t>2026-10-17T06:14:12+00:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ecf15066-1933-4b3a-8eb9-3221d01638f6</t>
+          <t>369cfc3a-930d-4786-b061-a9499455a895</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8016,29 +8016,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-17T06:14:01+00:00</t>
+          <t>2026-10-17T06:13:49+00:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ecf15066-1933-4b3a-8eb9-3221d01638f6</t>
+          <t>369cfc3a-930d-4786-b061-a9499455a895</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8048,34 +8048,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-17T06:14:03+00:00</t>
+          <t>2026-10-17T06:14:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ecf15066-1933-4b3a-8eb9-3221d01638f6</t>
+          <t>369cfc3a-930d-4786-b061-a9499455a895</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -8105,14 +8105,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-17T06:14:12+00:00</t>
+          <t>2026-10-17T06:15:12+00:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>369cfc3a-930d-4786-b061-a9499455a895</t>
+          <t>97dff2b2-8899-49a8-a287-79551ec1cf6a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8127,29 +8127,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-17T06:13:49+00:00</t>
+          <t>2026-10-17T06:15:47+00:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>369cfc3a-930d-4786-b061-a9499455a895</t>
+          <t>97dff2b2-8899-49a8-a287-79551ec1cf6a</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8164,29 +8164,29 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-17T06:14:48+00:00</t>
+          <t>2026-10-17T06:16:02+00:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>369cfc3a-930d-4786-b061-a9499455a895</t>
+          <t>97dff2b2-8899-49a8-a287-79551ec1cf6a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -8211,19 +8211,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-17T06:15:12+00:00</t>
+          <t>2026-10-17T06:16:22+00:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>97dff2b2-8899-49a8-a287-79551ec1cf6a</t>
+          <t>8527afca-ee6c-4f39-8a78-c280af8f3c8d</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8233,34 +8233,34 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-17T06:15:47+00:00</t>
+          <t>2026-10-17T06:28:12+00:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>97dff2b2-8899-49a8-a287-79551ec1cf6a</t>
+          <t>8527afca-ee6c-4f39-8a78-c280af8f3c8d</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -8280,24 +8280,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-17T06:16:02+00:00</t>
+          <t>2026-10-17T06:28:39+00:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>97dff2b2-8899-49a8-a287-79551ec1cf6a</t>
+          <t>8527afca-ee6c-4f39-8a78-c280af8f3c8d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8312,29 +8312,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-17T06:16:22+00:00</t>
+          <t>2026-10-17T06:28:54+00:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8527afca-ee6c-4f39-8a78-c280af8f3c8d</t>
+          <t>c02bf9e6-ab59-4ca9-a1df-e25af9486f18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8344,12 +8344,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -8359,19 +8359,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-17T06:28:12+00:00</t>
+          <t>2026-10-17T06:29:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8527afca-ee6c-4f39-8a78-c280af8f3c8d</t>
+          <t>c02bf9e6-ab59-4ca9-a1df-e25af9486f18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -8396,19 +8396,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-17T06:28:39+00:00</t>
+          <t>2026-10-17T06:29:56+00:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8527afca-ee6c-4f39-8a78-c280af8f3c8d</t>
+          <t>c02bf9e6-ab59-4ca9-a1df-e25af9486f18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -8438,14 +8438,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-17T06:28:54+00:00</t>
+          <t>2026-10-17T06:30:07+00:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>c02bf9e6-ab59-4ca9-a1df-e25af9486f18</t>
+          <t>9204f951-17ad-4906-8464-8d184c63d414</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8455,17 +8455,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -8475,14 +8475,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-17T06:29:44+00:00</t>
+          <t>2026-10-17T07:52:40+00:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>c02bf9e6-ab59-4ca9-a1df-e25af9486f18</t>
+          <t>9204f951-17ad-4906-8464-8d184c63d414</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8507,19 +8507,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-10-17T06:29:56+00:00</t>
+          <t>2026-10-17T07:53:15+00:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>c02bf9e6-ab59-4ca9-a1df-e25af9486f18</t>
+          <t>9204f951-17ad-4906-8464-8d184c63d414</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -8544,19 +8544,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-17T06:30:07+00:00</t>
+          <t>2026-10-17T07:53:46+00:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9204f951-17ad-4906-8464-8d184c63d414</t>
+          <t>584ebf7b-ad73-47e9-87c4-54b9d2dc3a31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8571,29 +8571,29 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-17T07:52:40+00:00</t>
+          <t>2026-10-17T19:08:37+00:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9204f951-17ad-4906-8464-8d184c63d414</t>
+          <t>584ebf7b-ad73-47e9-87c4-54b9d2dc3a31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8608,29 +8608,29 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-17T07:53:15+00:00</t>
+          <t>2026-10-17T19:08:54+00:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9204f951-17ad-4906-8464-8d184c63d414</t>
+          <t>584ebf7b-ad73-47e9-87c4-54b9d2dc3a31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8645,29 +8645,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-17T07:53:46+00:00</t>
+          <t>2026-10-17T19:09:21+00:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1462968c-4df5-4f38-88f4-fe2cf6851998</t>
+          <t>0493eb42-6292-4d55-8079-cc43729613b3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8677,34 +8677,34 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-17T10:17:11+00:00</t>
+          <t>2026-10-17T19:14:06+00:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1462968c-4df5-4f38-88f4-fe2cf6851998</t>
+          <t>0493eb42-6292-4d55-8079-cc43729613b3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8714,34 +8714,34 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-10-17T10:17:45+00:00</t>
+          <t>2026-10-17T19:14:57+00:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1462968c-4df5-4f38-88f4-fe2cf6851998</t>
+          <t>0493eb42-6292-4d55-8079-cc43729613b3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8756,29 +8756,29 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-17T10:18:06+00:00</t>
+          <t>2026-10-17T19:15:28+00:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>584ebf7b-ad73-47e9-87c4-54b9d2dc3a31</t>
+          <t>99b44256-68aa-41ac-b9c5-369356bff5da</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8793,29 +8793,29 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-17T19:08:37+00:00</t>
+          <t>2026-10-18T05:10:05+00:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>584ebf7b-ad73-47e9-87c4-54b9d2dc3a31</t>
+          <t>99b44256-68aa-41ac-b9c5-369356bff5da</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -8845,14 +8845,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-17T19:08:54+00:00</t>
+          <t>2026-10-18T05:11:18+00:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>584ebf7b-ad73-47e9-87c4-54b9d2dc3a31</t>
+          <t>99b44256-68aa-41ac-b9c5-369356bff5da</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8867,29 +8867,29 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-17T19:09:21+00:00</t>
+          <t>2026-10-18T05:12:24+00:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0493eb42-6292-4d55-8079-cc43729613b3</t>
+          <t>5e1b260a-2ae2-49d2-83ca-8f452c0bc3f0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8899,17 +8899,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -8919,14 +8919,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-17T19:14:06+00:00</t>
+          <t>2026-10-18T05:37:03+00:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0493eb42-6292-4d55-8079-cc43729613b3</t>
+          <t>5e1b260a-2ae2-49d2-83ca-8f452c0bc3f0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -8941,29 +8941,29 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-17T19:14:57+00:00</t>
+          <t>2026-10-18T05:37:15+00:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0493eb42-6292-4d55-8079-cc43729613b3</t>
+          <t>5e1b260a-2ae2-49d2-83ca-8f452c0bc3f0</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8973,34 +8973,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-17T19:15:28+00:00</t>
+          <t>2026-10-18T05:37:24+00:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>f6c2dbd1-3448-43ea-9e09-10d3a794f2c6</t>
+          <t>aef9d24e-9d0c-4302-855c-e70c6cee660c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9010,34 +9010,34 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-17T23:49:49+00:00</t>
+          <t>2026-10-18T10:16:35+00:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>f6c2dbd1-3448-43ea-9e09-10d3a794f2c6</t>
+          <t>aef9d24e-9d0c-4302-855c-e70c6cee660c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9057,24 +9057,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-17T23:50:09+00:00</t>
+          <t>2026-10-18T10:16:53+00:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>f6c2dbd1-3448-43ea-9e09-10d3a794f2c6</t>
+          <t>aef9d24e-9d0c-4302-855c-e70c6cee660c</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9089,29 +9089,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-10-17T23:50:37+00:00</t>
+          <t>2026-10-18T10:17:07+00:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>99b44256-68aa-41ac-b9c5-369356bff5da</t>
+          <t>544c0530-6a56-4e22-8210-e4492be71d51</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -9136,19 +9136,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-10-18T05:10:05+00:00</t>
+          <t>2026-10-21T09:20:22+00:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>99b44256-68aa-41ac-b9c5-369356bff5da</t>
+          <t>544c0530-6a56-4e22-8210-e4492be71d51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9168,24 +9168,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-10-18T05:11:18+00:00</t>
+          <t>2026-10-18T11:24:54+00:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>99b44256-68aa-41ac-b9c5-369356bff5da</t>
+          <t>544c0530-6a56-4e22-8210-e4492be71d51</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -9215,14 +9215,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-10-18T05:12:24+00:00</t>
+          <t>2026-10-16T23:30:54+00:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5e1b260a-2ae2-49d2-83ca-8f452c0bc3f0</t>
+          <t>aefba00f-ffa3-4d64-91c8-4f2cbf3efe97</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -9252,14 +9252,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-10-18T05:37:03+00:00</t>
+          <t>2026-10-19T14:09:10+00:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5e1b260a-2ae2-49d2-83ca-8f452c0bc3f0</t>
+          <t>aefba00f-ffa3-4d64-91c8-4f2cbf3efe97</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9269,34 +9269,34 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-10-18T05:37:15+00:00</t>
+          <t>2026-10-20T14:41:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5e1b260a-2ae2-49d2-83ca-8f452c0bc3f0</t>
+          <t>aefba00f-ffa3-4d64-91c8-4f2cbf3efe97</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9306,34 +9306,34 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-18T05:37:24+00:00</t>
+          <t>2026-10-17T15:10:07+00:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>aef9d24e-9d0c-4302-855c-e70c6cee660c</t>
+          <t>dcc41750-23a1-46cf-8c51-59edac35dc58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -9363,14 +9363,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-10-18T10:16:35+00:00</t>
+          <t>2026-10-19T13:11:27+00:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>aef9d24e-9d0c-4302-855c-e70c6cee660c</t>
+          <t>dcc41750-23a1-46cf-8c51-59edac35dc58</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9395,19 +9395,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-10-18T10:16:53+00:00</t>
+          <t>2026-10-18T16:28:36+00:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>aef9d24e-9d0c-4302-855c-e70c6cee660c</t>
+          <t>dcc41750-23a1-46cf-8c51-59edac35dc58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9427,24 +9427,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-10-18T10:17:07+00:00</t>
+          <t>2026-10-18T06:52:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>544c0530-6a56-4e22-8210-e4492be71d51</t>
+          <t>14905293-b3c0-4640-83ab-38f927b384c7</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9459,29 +9459,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-10-21T09:20:22+00:00</t>
+          <t>2026-10-16T16:06:19+00:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>544c0530-6a56-4e22-8210-e4492be71d51</t>
+          <t>14905293-b3c0-4640-83ab-38f927b384c7</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9491,34 +9491,34 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-10-18T11:24:54+00:00</t>
+          <t>2026-10-21T10:46:13+00:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>544c0530-6a56-4e22-8210-e4492be71d51</t>
+          <t>14905293-b3c0-4640-83ab-38f927b384c7</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9528,34 +9528,34 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-10-16T23:30:54+00:00</t>
+          <t>2026-10-19T12:01:11+00:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ffb5392a-6cf3-4c1c-9dfa-03147eb5c62b</t>
+          <t>7dd8c3d7-55eb-4a9a-8d4e-dd8fbab2e051</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9575,24 +9575,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-10-21T01:09:54+00:00</t>
+          <t>2026-10-20T03:12:38+00:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ffb5392a-6cf3-4c1c-9dfa-03147eb5c62b</t>
+          <t>7dd8c3d7-55eb-4a9a-8d4e-dd8fbab2e051</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9602,34 +9602,34 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-10-20T21:47:21+00:00</t>
+          <t>2026-10-19T18:54:43+00:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ffb5392a-6cf3-4c1c-9dfa-03147eb5c62b</t>
+          <t>7dd8c3d7-55eb-4a9a-8d4e-dd8fbab2e051</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9639,17 +9639,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -9659,14 +9659,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-10-17T09:30:21+00:00</t>
+          <t>2026-10-18T17:12:38+00:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>aefba00f-ffa3-4d64-91c8-4f2cbf3efe97</t>
+          <t>c93fe90f-14aa-4dbe-82eb-fe6d1fb8e714</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9686,24 +9686,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-10-19T14:09:10+00:00</t>
+          <t>2026-10-19T09:35:23+00:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>aefba00f-ffa3-4d64-91c8-4f2cbf3efe97</t>
+          <t>c93fe90f-14aa-4dbe-82eb-fe6d1fb8e714</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9713,34 +9713,34 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-10-20T14:41:55+00:00</t>
+          <t>2026-10-20T01:23:37+00:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>aefba00f-ffa3-4d64-91c8-4f2cbf3efe97</t>
+          <t>c93fe90f-14aa-4dbe-82eb-fe6d1fb8e714</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -9765,19 +9765,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-10-17T15:10:07+00:00</t>
+          <t>2026-10-17T07:08:41+00:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dcc41750-23a1-46cf-8c51-59edac35dc58</t>
+          <t>3256610e-c690-4bdc-b178-109055c06a70</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -9807,14 +9807,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-10-19T13:11:27+00:00</t>
+          <t>2026-10-20T17:08:58+00:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dcc41750-23a1-46cf-8c51-59edac35dc58</t>
+          <t>3256610e-c690-4bdc-b178-109055c06a70</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -9844,14 +9844,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-18T16:28:36+00:00</t>
+          <t>2026-10-19T19:04:37+00:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dcc41750-23a1-46cf-8c51-59edac35dc58</t>
+          <t>3256610e-c690-4bdc-b178-109055c06a70</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9861,34 +9861,34 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-10-18T06:52:17+00:00</t>
+          <t>2026-10-16T14:17:01+00:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>22829758-9e77-4f20-87b8-4b4c4f08de3c</t>
+          <t>1d6a2c6d-ef86-47ae-b35d-5ae7026c04b1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9898,17 +9898,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -9918,14 +9918,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-10-19T11:50:24+00:00</t>
+          <t>2026-10-17T11:44:50+00:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>22829758-9e77-4f20-87b8-4b4c4f08de3c</t>
+          <t>1d6a2c6d-ef86-47ae-b35d-5ae7026c04b1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9950,19 +9950,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-10-19T15:10:33+00:00</t>
+          <t>2026-10-17T01:03:37+00:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>22829758-9e77-4f20-87b8-4b4c4f08de3c</t>
+          <t>1d6a2c6d-ef86-47ae-b35d-5ae7026c04b1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9972,34 +9972,34 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-10-17T11:56:34+00:00</t>
+          <t>2026-10-20T19:29:53+00:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>14905293-b3c0-4640-83ab-38f927b384c7</t>
+          <t>08c6d687-877c-4d39-94ec-dd66e50d4d0e</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10009,34 +10009,34 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-10-16T16:06:19+00:00</t>
+          <t>2026-10-21T03:32:32+00:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>14905293-b3c0-4640-83ab-38f927b384c7</t>
+          <t>08c6d687-877c-4d39-94ec-dd66e50d4d0e</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10046,34 +10046,34 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-10-21T10:46:13+00:00</t>
+          <t>2026-10-18T01:36:00+00:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>14905293-b3c0-4640-83ab-38f927b384c7</t>
+          <t>08c6d687-877c-4d39-94ec-dd66e50d4d0e</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -10098,19 +10098,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-10-19T12:01:11+00:00</t>
+          <t>2026-10-17T20:30:56+00:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7dd8c3d7-55eb-4a9a-8d4e-dd8fbab2e051</t>
+          <t>e4d1c987-d597-481e-acf0-d6a91569f899</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -10140,14 +10140,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-10-20T03:12:38+00:00</t>
+          <t>2026-10-16T06:30:58+00:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7dd8c3d7-55eb-4a9a-8d4e-dd8fbab2e051</t>
+          <t>e4d1c987-d597-481e-acf0-d6a91569f899</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -10172,19 +10172,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-10-19T18:54:43+00:00</t>
+          <t>2026-10-17T05:31:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>7dd8c3d7-55eb-4a9a-8d4e-dd8fbab2e051</t>
+          <t>e4d1c987-d597-481e-acf0-d6a91569f899</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10199,29 +10199,29 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-10-18T17:12:38+00:00</t>
+          <t>2026-10-16T07:24:29+00:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>c93fe90f-14aa-4dbe-82eb-fe6d1fb8e714</t>
+          <t>8552ad88-e15b-4260-8699-eca64416451d</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10231,12 +10231,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -10246,19 +10246,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-10-19T09:35:23+00:00</t>
+          <t>2026-10-18T09:30:29+00:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>c93fe90f-14aa-4dbe-82eb-fe6d1fb8e714</t>
+          <t>8552ad88-e15b-4260-8699-eca64416451d</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10268,17 +10268,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10288,14 +10288,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-10-20T01:23:37+00:00</t>
+          <t>2026-10-20T00:23:25+00:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>c93fe90f-14aa-4dbe-82eb-fe6d1fb8e714</t>
+          <t>8552ad88-e15b-4260-8699-eca64416451d</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10305,17 +10305,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10325,14 +10325,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-10-17T07:08:41+00:00</t>
+          <t>2026-10-17T05:39:57+00:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>e7ff5aac-9648-4c76-bcbc-40198bfdbea8</t>
+          <t>9c1290c4-2694-4cb7-8cde-257830e6e64c</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10342,34 +10342,34 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-10-18T23:35:35+00:00</t>
+          <t>2026-10-17T14:23:39+00:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>e7ff5aac-9648-4c76-bcbc-40198bfdbea8</t>
+          <t>9c1290c4-2694-4cb7-8cde-257830e6e64c</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10384,29 +10384,29 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-10-21T10:52:15+00:00</t>
+          <t>2026-10-21T05:29:57+00:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>e7ff5aac-9648-4c76-bcbc-40198bfdbea8</t>
+          <t>9c1290c4-2694-4cb7-8cde-257830e6e64c</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10436,14 +10436,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-10-17T23:31:24+00:00</t>
+          <t>2026-10-17T10:07:35+00:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3256610e-c690-4bdc-b178-109055c06a70</t>
+          <t>77e3d2cf-4842-41f3-9951-14e60f50f7c8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10453,34 +10453,34 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-10-20T17:08:58+00:00</t>
+          <t>2026-10-19T20:52:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3256610e-c690-4bdc-b178-109055c06a70</t>
+          <t>77e3d2cf-4842-41f3-9951-14e60f50f7c8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10490,34 +10490,34 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-10-19T19:04:37+00:00</t>
+          <t>2026-10-19T22:17:08+00:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3256610e-c690-4bdc-b178-109055c06a70</t>
+          <t>77e3d2cf-4842-41f3-9951-14e60f50f7c8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10527,34 +10527,34 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-10-16T14:17:01+00:00</t>
+          <t>2026-10-17T09:40:56+00:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1d6a2c6d-ef86-47ae-b35d-5ae7026c04b1</t>
+          <t>bf93c304-5780-4b42-a41b-90b1c88a5f85</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -10579,19 +10579,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-10-17T11:44:50+00:00</t>
+          <t>2026-10-20T07:07:23+00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1d6a2c6d-ef86-47ae-b35d-5ae7026c04b1</t>
+          <t>bf93c304-5780-4b42-a41b-90b1c88a5f85</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10606,12 +10606,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10621,14 +10621,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-10-17T01:03:37+00:00</t>
+          <t>2026-10-17T00:32:15+00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1d6a2c6d-ef86-47ae-b35d-5ae7026c04b1</t>
+          <t>bf93c304-5780-4b42-a41b-90b1c88a5f85</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10643,29 +10643,29 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-10-20T19:29:53+00:00</t>
+          <t>2026-10-20T18:57:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>08c6d687-877c-4d39-94ec-dd66e50d4d0e</t>
+          <t>84799f98-8811-49f2-ae1b-845f708dae0b</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10685,24 +10685,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-10-21T03:32:32+00:00</t>
+          <t>2026-10-17T06:42:47+00:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>08c6d687-877c-4d39-94ec-dd66e50d4d0e</t>
+          <t>84799f98-8811-49f2-ae1b-845f708dae0b</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10712,34 +10712,34 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-10-18T01:36:00+00:00</t>
+          <t>2026-10-20T00:11:11+00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>08c6d687-877c-4d39-94ec-dd66e50d4d0e</t>
+          <t>84799f98-8811-49f2-ae1b-845f708dae0b</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10749,34 +10749,34 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-10-17T20:30:56+00:00</t>
+          <t>2026-10-20T07:58:58+00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>e4d1c987-d597-481e-acf0-d6a91569f899</t>
+          <t>3a99bf3b-de45-4452-9bd6-1fd0404bab8a</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -10806,14 +10806,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-10-16T06:30:58+00:00</t>
+          <t>2026-10-20T19:22:01+00:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>e4d1c987-d597-481e-acf0-d6a91569f899</t>
+          <t>3a99bf3b-de45-4452-9bd6-1fd0404bab8a</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -10843,14 +10843,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-10-17T05:31:55+00:00</t>
+          <t>2026-10-17T13:52:15+00:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>e4d1c987-d597-481e-acf0-d6a91569f899</t>
+          <t>3a99bf3b-de45-4452-9bd6-1fd0404bab8a</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10865,29 +10865,29 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-10-16T07:24:29+00:00</t>
+          <t>2026-10-16T13:18:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8552ad88-e15b-4260-8699-eca64416451d</t>
+          <t>b3dffb0f-80dd-4622-9c50-53d3e6f8db46</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10907,24 +10907,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-10-18T09:30:29+00:00</t>
+          <t>2026-10-20T18:18:09+00:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8552ad88-e15b-4260-8699-eca64416451d</t>
+          <t>b3dffb0f-80dd-4622-9c50-53d3e6f8db46</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10934,34 +10934,34 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-10-20T00:23:25+00:00</t>
+          <t>2026-10-21T08:18:50+00:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8552ad88-e15b-4260-8699-eca64416451d</t>
+          <t>b3dffb0f-80dd-4622-9c50-53d3e6f8db46</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10971,17 +10971,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -10991,14 +10991,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-10-17T05:39:57+00:00</t>
+          <t>2026-10-20T01:16:36+00:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>9c1290c4-2694-4cb7-8cde-257830e6e64c</t>
+          <t>c27dabb1-ea92-474e-b225-379a6796ef70</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -11013,29 +11013,29 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-10-17T14:23:39+00:00</t>
+          <t>2026-10-18T14:43:18+00:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>9c1290c4-2694-4cb7-8cde-257830e6e64c</t>
+          <t>c27dabb1-ea92-474e-b225-379a6796ef70</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -11055,24 +11055,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-10-21T05:29:57+00:00</t>
+          <t>2026-10-21T10:46:14+00:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>9c1290c4-2694-4cb7-8cde-257830e6e64c</t>
+          <t>c27dabb1-ea92-474e-b225-379a6796ef70</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -11097,19 +11097,19 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-10-17T10:07:35+00:00</t>
+          <t>2026-10-18T09:13:42+00:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>77e3d2cf-4842-41f3-9951-14e60f50f7c8</t>
+          <t>da27b61b-beef-4ca9-a325-d3e1051fdb75</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11134,19 +11134,19 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-10-19T20:52:55+00:00</t>
+          <t>2026-10-17T00:35:13+00:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>77e3d2cf-4842-41f3-9951-14e60f50f7c8</t>
+          <t>da27b61b-beef-4ca9-a325-d3e1051fdb75</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11156,34 +11156,34 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-10-19T22:17:08+00:00</t>
+          <t>2026-10-19T20:12:02+00:00</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>77e3d2cf-4842-41f3-9951-14e60f50f7c8</t>
+          <t>da27b61b-beef-4ca9-a325-d3e1051fdb75</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11193,34 +11193,34 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-10-17T09:40:56+00:00</t>
+          <t>2026-10-17T01:45:45+00:00</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bf93c304-5780-4b42-a41b-90b1c88a5f85</t>
+          <t>fd39725f-255d-4e23-8cf8-541685e9ff31</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11235,29 +11235,29 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-10-20T07:07:23+00:00</t>
+          <t>2026-10-17T14:39:16+00:00</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>bf93c304-5780-4b42-a41b-90b1c88a5f85</t>
+          <t>fd39725f-255d-4e23-8cf8-541685e9ff31</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11272,29 +11272,29 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-10-17T00:32:15+00:00</t>
+          <t>2026-10-20T19:50:35+00:00</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>bf93c304-5780-4b42-a41b-90b1c88a5f85</t>
+          <t>fd39725f-255d-4e23-8cf8-541685e9ff31</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11309,29 +11309,29 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-10-20T18:57:17+00:00</t>
+          <t>2026-10-20T00:29:18+00:00</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>84799f98-8811-49f2-ae1b-845f708dae0b</t>
+          <t>4c50cf74-51ef-4b62-a355-ea1de2b21eb9</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11341,17 +11341,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -11361,14 +11361,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-10-17T06:42:47+00:00</t>
+          <t>2026-10-19T17:51:23+00:00</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>84799f98-8811-49f2-ae1b-845f708dae0b</t>
+          <t>4c50cf74-51ef-4b62-a355-ea1de2b21eb9</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11378,34 +11378,34 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-10-20T00:11:11+00:00</t>
+          <t>2026-10-20T14:07:53+00:00</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>84799f98-8811-49f2-ae1b-845f708dae0b</t>
+          <t>4c50cf74-51ef-4b62-a355-ea1de2b21eb9</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11415,34 +11415,34 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-10-20T07:58:58+00:00</t>
+          <t>2026-10-17T17:22:03+00:00</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3a99bf3b-de45-4452-9bd6-1fd0404bab8a</t>
+          <t>b0ca7161-23d6-4b6d-a1fb-29df4b59a9ce</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11452,34 +11452,34 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-10-20T19:22:01+00:00</t>
+          <t>2026-10-18T10:44:50+00:00</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3a99bf3b-de45-4452-9bd6-1fd0404bab8a</t>
+          <t>b0ca7161-23d6-4b6d-a1fb-29df4b59a9ce</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11489,17 +11489,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -11509,14 +11509,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-10-17T13:52:15+00:00</t>
+          <t>2026-10-18T21:25:20+00:00</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3a99bf3b-de45-4452-9bd6-1fd0404bab8a</t>
+          <t>b0ca7161-23d6-4b6d-a1fb-29df4b59a9ce</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11541,19 +11541,19 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-10-16T13:18:48+00:00</t>
+          <t>2026-10-19T23:41:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>b3dffb0f-80dd-4622-9c50-53d3e6f8db46</t>
+          <t>e4d5d02d-e7fe-4496-a3b4-ba5b0428c48b</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11563,34 +11563,34 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-10-20T18:18:09+00:00</t>
+          <t>2026-10-21T09:55:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>b3dffb0f-80dd-4622-9c50-53d3e6f8db46</t>
+          <t>e4d5d02d-e7fe-4496-a3b4-ba5b0428c48b</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -11620,14 +11620,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-10-21T08:18:50+00:00</t>
+          <t>2026-10-17T19:37:31+00:00</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>b3dffb0f-80dd-4622-9c50-53d3e6f8db46</t>
+          <t>e4d5d02d-e7fe-4496-a3b4-ba5b0428c48b</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11637,34 +11637,34 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-10-20T01:16:36+00:00</t>
+          <t>2026-10-17T22:14:04+00:00</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>c27dabb1-ea92-474e-b225-379a6796ef70</t>
+          <t>fefb4180-9c9c-4395-88ef-7aaf641db996</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11674,34 +11674,34 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-10-18T14:43:18+00:00</t>
+          <t>2026-10-18T11:44:32+00:00</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>c27dabb1-ea92-474e-b225-379a6796ef70</t>
+          <t>fefb4180-9c9c-4395-88ef-7aaf641db996</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11726,19 +11726,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-10-21T10:46:14+00:00</t>
+          <t>2026-10-20T18:38:04+00:00</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>c27dabb1-ea92-474e-b225-379a6796ef70</t>
+          <t>fefb4180-9c9c-4395-88ef-7aaf641db996</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11758,24 +11758,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-10-18T09:13:42+00:00</t>
+          <t>2026-10-18T02:39:18+00:00</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>da27b61b-beef-4ca9-a325-d3e1051fdb75</t>
+          <t>403d1af2-6fb2-4d88-8b14-7f912b9de368</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11790,29 +11790,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-10-17T00:35:13+00:00</t>
+          <t>2026-10-17T15:07:46+00:00</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>da27b61b-beef-4ca9-a325-d3e1051fdb75</t>
+          <t>403d1af2-6fb2-4d88-8b14-7f912b9de368</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11832,24 +11832,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-10-19T20:12:02+00:00</t>
+          <t>2026-10-17T00:26:05+00:00</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>da27b61b-beef-4ca9-a325-d3e1051fdb75</t>
+          <t>403d1af2-6fb2-4d88-8b14-7f912b9de368</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -11879,14 +11879,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-10-17T01:45:45+00:00</t>
+          <t>2026-10-20T11:34:07+00:00</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>fd39725f-255d-4e23-8cf8-541685e9ff31</t>
+          <t>743c05ff-96b6-4047-b779-57128b6e253c</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11911,19 +11911,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-10-17T14:39:16+00:00</t>
+          <t>2026-10-17T04:05:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>fd39725f-255d-4e23-8cf8-541685e9ff31</t>
+          <t>743c05ff-96b6-4047-b779-57128b6e253c</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11933,34 +11933,34 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-10-20T19:50:35+00:00</t>
+          <t>2026-10-17T18:08:43+00:00</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>fd39725f-255d-4e23-8cf8-541685e9ff31</t>
+          <t>743c05ff-96b6-4047-b779-57128b6e253c</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11975,29 +11975,29 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-10-20T00:29:18+00:00</t>
+          <t>2026-10-21T01:09:35+00:00</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4c50cf74-51ef-4b62-a355-ea1de2b21eb9</t>
+          <t>749de868-e34c-4654-a6dc-870b89cc2d16</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12007,17 +12007,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -12027,14 +12027,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-10-19T17:51:23+00:00</t>
+          <t>2026-10-16T16:55:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4c50cf74-51ef-4b62-a355-ea1de2b21eb9</t>
+          <t>749de868-e34c-4654-a6dc-870b89cc2d16</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12049,29 +12049,29 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-10-20T14:07:53+00:00</t>
+          <t>2026-10-19T02:26:09+00:00</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4c50cf74-51ef-4b62-a355-ea1de2b21eb9</t>
+          <t>749de868-e34c-4654-a6dc-870b89cc2d16</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12081,34 +12081,34 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-10-17T17:22:03+00:00</t>
+          <t>2026-10-20T12:22:47+00:00</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>b0ca7161-23d6-4b6d-a1fb-29df4b59a9ce</t>
+          <t>873fa18d-72b7-4443-86c9-4baef7c83996</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12128,24 +12128,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-10-18T10:44:50+00:00</t>
+          <t>2026-10-19T20:39:34+00:00</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>b0ca7161-23d6-4b6d-a1fb-29df4b59a9ce</t>
+          <t>873fa18d-72b7-4443-86c9-4baef7c83996</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12170,19 +12170,19 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-10-18T21:25:20+00:00</t>
+          <t>2026-10-17T00:06:37+00:00</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>b0ca7161-23d6-4b6d-a1fb-29df4b59a9ce</t>
+          <t>873fa18d-72b7-4443-86c9-4baef7c83996</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12192,34 +12192,34 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-10-19T23:41:55+00:00</t>
+          <t>2026-10-17T21:38:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>e4d5d02d-e7fe-4496-a3b4-ba5b0428c48b</t>
+          <t>c959c23f-e9fc-4cd5-a40a-50db35d0e604</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12229,17 +12229,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -12249,14 +12249,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-10-21T09:55:44+00:00</t>
+          <t>2026-10-19T02:31:17+00:00</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>e4d5d02d-e7fe-4496-a3b4-ba5b0428c48b</t>
+          <t>c959c23f-e9fc-4cd5-a40a-50db35d0e604</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12281,19 +12281,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-10-17T19:37:31+00:00</t>
+          <t>2026-10-19T19:14:41+00:00</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>e4d5d02d-e7fe-4496-a3b4-ba5b0428c48b</t>
+          <t>c959c23f-e9fc-4cd5-a40a-50db35d0e604</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12303,34 +12303,34 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-10-17T22:14:04+00:00</t>
+          <t>2026-10-19T02:27:00+00:00</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>fefb4180-9c9c-4395-88ef-7aaf641db996</t>
+          <t>e2e8ca74-d98c-46e0-8b7a-40d04e23856d</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12355,19 +12355,19 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-10-18T11:44:32+00:00</t>
+          <t>2026-10-21T06:08:19+00:00</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>fefb4180-9c9c-4395-88ef-7aaf641db996</t>
+          <t>e2e8ca74-d98c-46e0-8b7a-40d04e23856d</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -12397,14 +12397,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-10-20T18:38:04+00:00</t>
+          <t>2026-10-18T18:11:00+00:00</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>fefb4180-9c9c-4395-88ef-7aaf641db996</t>
+          <t>e2e8ca74-d98c-46e0-8b7a-40d04e23856d</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12419,12 +12419,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -12434,14 +12434,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-10-18T02:39:18+00:00</t>
+          <t>2026-10-19T06:35:53+00:00</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>403d1af2-6fb2-4d88-8b14-7f912b9de368</t>
+          <t>3c057273-9038-4411-b3bc-b90d6635dede</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12451,34 +12451,34 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+00:00</t>
+          <t>2026-10-19T01:12:11+00:00</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>403d1af2-6fb2-4d88-8b14-7f912b9de368</t>
+          <t>3c057273-9038-4411-b3bc-b90d6635dede</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12498,24 +12498,24 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-10-17T00:26:05+00:00</t>
+          <t>2026-10-20T14:21:46+00:00</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>403d1af2-6fb2-4d88-8b14-7f912b9de368</t>
+          <t>3c057273-9038-4411-b3bc-b90d6635dede</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -12545,14 +12545,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-10-20T11:34:07+00:00</t>
+          <t>2026-10-19T04:16:08+00:00</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>743c05ff-96b6-4047-b779-57128b6e253c</t>
+          <t>59d2aa2f-3b2e-48f2-83a7-66216147a092</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12562,34 +12562,34 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-10-17T04:05:48+00:00</t>
+          <t>2026-10-19T18:27:26+00:00</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>743c05ff-96b6-4047-b779-57128b6e253c</t>
+          <t>59d2aa2f-3b2e-48f2-83a7-66216147a092</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12599,34 +12599,34 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-10-17T18:08:43+00:00</t>
+          <t>2026-10-19T12:26:11+00:00</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>743c05ff-96b6-4047-b779-57128b6e253c</t>
+          <t>59d2aa2f-3b2e-48f2-83a7-66216147a092</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -12656,14 +12656,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-10-21T01:09:35+00:00</t>
+          <t>2026-10-18T12:56:06+00:00</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>749de868-e34c-4654-a6dc-870b89cc2d16</t>
+          <t>30b96da3-f5d7-4546-8584-6b03328405ca</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -12688,19 +12688,19 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-10-16T16:55:55+00:00</t>
+          <t>2026-10-19T06:08:14+00:00</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>749de868-e34c-4654-a6dc-870b89cc2d16</t>
+          <t>30b96da3-f5d7-4546-8584-6b03328405ca</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12710,34 +12710,34 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-10-19T02:26:09+00:00</t>
+          <t>2026-10-18T06:21:00+00:00</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>749de868-e34c-4654-a6dc-870b89cc2d16</t>
+          <t>30b96da3-f5d7-4546-8584-6b03328405ca</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12767,14 +12767,14 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-10-20T12:22:47+00:00</t>
+          <t>2026-10-19T10:35:49+00:00</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>873fa18d-72b7-4443-86c9-4baef7c83996</t>
+          <t>6fe55d6d-e7a4-4652-9c75-cc308831023f</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12799,19 +12799,19 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-10-19T20:39:34+00:00</t>
+          <t>2026-10-20T01:17:03+00:00</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>873fa18d-72b7-4443-86c9-4baef7c83996</t>
+          <t>6fe55d6d-e7a4-4652-9c75-cc308831023f</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12841,14 +12841,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-10-17T00:06:37+00:00</t>
+          <t>2026-10-16T11:13:41+00:00</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>873fa18d-72b7-4443-86c9-4baef7c83996</t>
+          <t>6fe55d6d-e7a4-4652-9c75-cc308831023f</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12863,29 +12863,29 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-10-17T21:38:55+00:00</t>
+          <t>2026-10-17T23:51:09+00:00</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>c959c23f-e9fc-4cd5-a40a-50db35d0e604</t>
+          <t>bdeebebf-89f7-4147-bb61-911aedf9e96e</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12895,17 +12895,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -12915,14 +12915,14 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-10-19T02:31:17+00:00</t>
+          <t>2026-10-21T01:25:08+00:00</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>c959c23f-e9fc-4cd5-a40a-50db35d0e604</t>
+          <t>bdeebebf-89f7-4147-bb61-911aedf9e96e</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12932,17 +12932,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -12952,14 +12952,14 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-10-19T19:14:41+00:00</t>
+          <t>2026-10-18T13:42:43+00:00</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>c959c23f-e9fc-4cd5-a40a-50db35d0e604</t>
+          <t>bdeebebf-89f7-4147-bb61-911aedf9e96e</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -12989,14 +12989,14 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-10-19T02:27:00+00:00</t>
+          <t>2026-10-17T02:50:34+00:00</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>e2e8ca74-d98c-46e0-8b7a-40d04e23856d</t>
+          <t>d9073e6f-47f8-40d8-93b9-cd2c09ac0bca</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -13026,14 +13026,14 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-10-21T06:08:19+00:00</t>
+          <t>2026-10-18T14:01:30+00:00</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>e2e8ca74-d98c-46e0-8b7a-40d04e23856d</t>
+          <t>d9073e6f-47f8-40d8-93b9-cd2c09ac0bca</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13043,34 +13043,34 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-10-18T18:11:00+00:00</t>
+          <t>2026-10-18T10:16:37+00:00</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>e2e8ca74-d98c-46e0-8b7a-40d04e23856d</t>
+          <t>d9073e6f-47f8-40d8-93b9-cd2c09ac0bca</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13090,24 +13090,24 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-10-19T06:35:53+00:00</t>
+          <t>2026-10-21T06:52:58+00:00</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3c057273-9038-4411-b3bc-b90d6635dede</t>
+          <t>d796284d-cb85-4051-8272-ab35b141a39b</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13117,12 +13117,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -13132,19 +13132,19 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-10-19T01:12:11+00:00</t>
+          <t>2026-10-20T08:42:23+00:00</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3c057273-9038-4411-b3bc-b90d6635dede</t>
+          <t>d796284d-cb85-4051-8272-ab35b141a39b</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13154,34 +13154,34 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-10-20T14:21:46+00:00</t>
+          <t>2026-10-17T01:55:11+00:00</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3c057273-9038-4411-b3bc-b90d6635dede</t>
+          <t>d796284d-cb85-4051-8272-ab35b141a39b</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13196,29 +13196,29 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-10-19T04:16:08+00:00</t>
+          <t>2026-10-18T02:59:29+00:00</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>59d2aa2f-3b2e-48f2-83a7-66216147a092</t>
+          <t>a897fddf-6f36-4b6d-94cc-6a4f9c0851da</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13228,34 +13228,34 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-10-19T18:27:26+00:00</t>
+          <t>2026-10-21T03:27:12+00:00</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>59d2aa2f-3b2e-48f2-83a7-66216147a092</t>
+          <t>a897fddf-6f36-4b6d-94cc-6a4f9c0851da</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13265,17 +13265,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -13285,14 +13285,14 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-10-19T12:26:11+00:00</t>
+          <t>2026-10-19T02:12:20+00:00</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>59d2aa2f-3b2e-48f2-83a7-66216147a092</t>
+          <t>a897fddf-6f36-4b6d-94cc-6a4f9c0851da</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13302,34 +13302,34 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-10-18T12:56:06+00:00</t>
+          <t>2026-10-21T11:16:01+00:00</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>30b96da3-f5d7-4546-8584-6b03328405ca</t>
+          <t>dc15ef4a-f134-461f-a298-901007984cae</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13344,29 +13344,29 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-10-19T06:08:14+00:00</t>
+          <t>2026-10-20T08:16:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>30b96da3-f5d7-4546-8584-6b03328405ca</t>
+          <t>dc15ef4a-f134-461f-a298-901007984cae</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -13391,19 +13391,19 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-10-18T06:21:00+00:00</t>
+          <t>2026-10-19T15:45:39+00:00</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>30b96da3-f5d7-4546-8584-6b03328405ca</t>
+          <t>dc15ef4a-f134-461f-a298-901007984cae</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13413,17 +13413,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -13433,14 +13433,14 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-10-19T10:35:49+00:00</t>
+          <t>2026-10-20T02:32:14+00:00</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>6fe55d6d-e7a4-4652-9c75-cc308831023f</t>
+          <t>25f65856-0cfd-431f-a79b-e75d88016b31</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13450,12 +13450,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -13465,19 +13465,19 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-10-20T01:17:03+00:00</t>
+          <t>2026-10-20T18:06:02+00:00</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>6fe55d6d-e7a4-4652-9c75-cc308831023f</t>
+          <t>25f65856-0cfd-431f-a79b-e75d88016b31</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13497,24 +13497,24 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-10-16T11:13:41+00:00</t>
+          <t>2026-10-21T07:24:55+00:00</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>6fe55d6d-e7a4-4652-9c75-cc308831023f</t>
+          <t>25f65856-0cfd-431f-a79b-e75d88016b31</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13524,12 +13524,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -13539,19 +13539,19 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-10-17T23:51:09+00:00</t>
+          <t>2026-10-16T10:45:52+00:00</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>bdeebebf-89f7-4147-bb61-911aedf9e96e</t>
+          <t>369804e0-ffb8-4dca-898a-4d029924048a</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13566,29 +13566,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-10-21T01:25:08+00:00</t>
+          <t>2026-10-17T12:53:24+00:00</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>bdeebebf-89f7-4147-bb61-911aedf9e96e</t>
+          <t>369804e0-ffb8-4dca-898a-4d029924048a</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13603,29 +13603,29 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-10-18T13:42:43+00:00</t>
+          <t>2026-10-21T00:35:06+00:00</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>bdeebebf-89f7-4147-bb61-911aedf9e96e</t>
+          <t>369804e0-ffb8-4dca-898a-4d029924048a</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13640,29 +13640,29 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-10-17T02:50:34+00:00</t>
+          <t>2026-10-17T11:53:06+00:00</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>d9073e6f-47f8-40d8-93b9-cd2c09ac0bca</t>
+          <t>bb2ddf0d-9f47-4361-b14a-3067d2f87dc9</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13677,14 +13677,14 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="F179" t="inlineStr">
         <is>
           <t>3</t>
@@ -13692,14 +13692,14 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-10-18T14:01:30+00:00</t>
+          <t>2026-10-17T01:11:42+00:00</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>d9073e6f-47f8-40d8-93b9-cd2c09ac0bca</t>
+          <t>bb2ddf0d-9f47-4361-b14a-3067d2f87dc9</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13709,17 +13709,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -13729,14 +13729,14 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-10-18T10:16:37+00:00</t>
+          <t>2026-10-18T05:09:09+00:00</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>d9073e6f-47f8-40d8-93b9-cd2c09ac0bca</t>
+          <t>bb2ddf0d-9f47-4361-b14a-3067d2f87dc9</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13746,12 +13746,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -13761,19 +13761,19 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-10-21T06:52:58+00:00</t>
+          <t>2026-10-18T19:18:24+00:00</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>d796284d-cb85-4051-8272-ab35b141a39b</t>
+          <t>230ce8a2-9370-40a1-8b30-a2aa6c2236db</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -13798,19 +13798,19 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-10-20T08:42:23+00:00</t>
+          <t>2026-10-21T09:23:48+00:00</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>d796284d-cb85-4051-8272-ab35b141a39b</t>
+          <t>230ce8a2-9370-40a1-8b30-a2aa6c2236db</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -13820,34 +13820,34 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-10-17T01:55:11+00:00</t>
+          <t>2026-10-18T22:35:54+00:00</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>d796284d-cb85-4051-8272-ab35b141a39b</t>
+          <t>230ce8a2-9370-40a1-8b30-a2aa6c2236db</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -13857,34 +13857,34 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-10-18T02:59:29+00:00</t>
+          <t>2026-10-16T15:33:56+00:00</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>a897fddf-6f36-4b6d-94cc-6a4f9c0851da</t>
+          <t>8e39762b-b862-408d-8502-aba46ab023f0</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -13894,34 +13894,34 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-10-21T03:27:12+00:00</t>
+          <t>2026-10-18T20:38:00+00:00</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>a897fddf-6f36-4b6d-94cc-6a4f9c0851da</t>
+          <t>8e39762b-b862-408d-8502-aba46ab023f0</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -13936,29 +13936,29 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-10-19T02:12:20+00:00</t>
+          <t>2026-10-19T00:02:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>a897fddf-6f36-4b6d-94cc-6a4f9c0851da</t>
+          <t>8e39762b-b862-408d-8502-aba46ab023f0</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -13978,24 +13978,24 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-10-21T11:16:01+00:00</t>
+          <t>2026-10-18T03:30:52+00:00</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>dc15ef4a-f134-461f-a298-901007984cae</t>
+          <t>f59b2607-a6e7-46ba-b490-4d518c4f33c8</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14005,17 +14005,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -14025,14 +14025,14 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-10-20T08:16:48+00:00</t>
+          <t>2026-10-21T13:13:41+00:00</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>dc15ef4a-f134-461f-a298-901007984cae</t>
+          <t>f59b2607-a6e7-46ba-b490-4d518c4f33c8</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14042,34 +14042,34 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-10-19T15:45:39+00:00</t>
+          <t>2026-10-20T15:00:43+00:00</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>dc15ef4a-f134-461f-a298-901007984cae</t>
+          <t>f59b2607-a6e7-46ba-b490-4d518c4f33c8</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14084,29 +14084,29 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-10-20T02:32:14+00:00</t>
+          <t>2026-10-16T21:05:16+00:00</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>25f65856-0cfd-431f-a79b-e75d88016b31</t>
+          <t>a11eb8b3-501d-4ee8-9054-39ff57433e6b</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14121,29 +14121,29 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-10-20T18:06:02+00:00</t>
+          <t>2026-10-20T05:48:13+00:00</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>25f65856-0cfd-431f-a79b-e75d88016b31</t>
+          <t>a11eb8b3-501d-4ee8-9054-39ff57433e6b</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14158,29 +14158,29 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-10-21T07:24:55+00:00</t>
+          <t>2026-10-20T12:20:16+00:00</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>25f65856-0cfd-431f-a79b-e75d88016b31</t>
+          <t>a11eb8b3-501d-4ee8-9054-39ff57433e6b</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14195,12 +14195,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -14210,14 +14210,14 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-10-16T10:45:52+00:00</t>
+          <t>2026-10-17T08:25:08+00:00</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>369804e0-ffb8-4dca-898a-4d029924048a</t>
+          <t>5571a61f-fbab-4aea-a84a-3aabbf728603</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14227,34 +14227,34 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-10-17T12:53:24+00:00</t>
+          <t>2026-10-17T04:39:28+00:00</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>369804e0-ffb8-4dca-898a-4d029924048a</t>
+          <t>5571a61f-fbab-4aea-a84a-3aabbf728603</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -14284,14 +14284,14 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-10-21T00:35:06+00:00</t>
+          <t>2026-10-17T21:37:40+00:00</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>369804e0-ffb8-4dca-898a-4d029924048a</t>
+          <t>5571a61f-fbab-4aea-a84a-3aabbf728603</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -14311,24 +14311,24 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-10-17T11:53:06+00:00</t>
+          <t>2026-10-18T18:19:11+00:00</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>bb2ddf0d-9f47-4361-b14a-3067d2f87dc9</t>
+          <t>f04f4893-fd8f-4a95-a551-29d2746862cf</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -14338,34 +14338,34 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-10-17T01:11:42+00:00</t>
+          <t>2026-10-17T01:24:18+00:00</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>bb2ddf0d-9f47-4361-b14a-3067d2f87dc9</t>
+          <t>f04f4893-fd8f-4a95-a551-29d2746862cf</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -14375,17 +14375,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -14395,14 +14395,14 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-10-18T05:09:09+00:00</t>
+          <t>2026-10-20T09:39:34+00:00</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>bb2ddf0d-9f47-4361-b14a-3067d2f87dc9</t>
+          <t>f04f4893-fd8f-4a95-a551-29d2746862cf</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -14412,34 +14412,34 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-10-18T19:18:24+00:00</t>
+          <t>2026-10-17T11:02:58+00:00</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>230ce8a2-9370-40a1-8b30-a2aa6c2236db</t>
+          <t>b8a565c9-994e-4cf6-b911-3421aef9b97c</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -14464,19 +14464,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-10-21T09:23:48+00:00</t>
+          <t>2026-10-21T00:48:24+00:00</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>230ce8a2-9370-40a1-8b30-a2aa6c2236db</t>
+          <t>b8a565c9-994e-4cf6-b911-3421aef9b97c</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -14491,12 +14491,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -14506,14 +14506,14 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-10-18T22:35:54+00:00</t>
+          <t>2026-10-17T04:10:36+00:00</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>230ce8a2-9370-40a1-8b30-a2aa6c2236db</t>
+          <t>b8a565c9-994e-4cf6-b911-3421aef9b97c</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -14528,12 +14528,12 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -14543,14 +14543,14 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-10-16T15:33:56+00:00</t>
+          <t>2026-10-16T18:04:57+00:00</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>8e39762b-b862-408d-8502-aba46ab023f0</t>
+          <t>e06d0613-79bd-40e2-8ef0-89ea67ae0a89</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -14575,19 +14575,19 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-10-18T20:38:00+00:00</t>
+          <t>2026-10-18T16:38:10+00:00</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8e39762b-b862-408d-8502-aba46ab023f0</t>
+          <t>e06d0613-79bd-40e2-8ef0-89ea67ae0a89</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -14597,34 +14597,34 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-10-19T00:02:44+00:00</t>
+          <t>2026-10-18T10:47:50+00:00</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>8e39762b-b862-408d-8502-aba46ab023f0</t>
+          <t>e06d0613-79bd-40e2-8ef0-89ea67ae0a89</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -14634,34 +14634,34 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-10-18T03:30:52+00:00</t>
+          <t>2026-10-17T10:50:50+00:00</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>f59b2607-a6e7-46ba-b490-4d518c4f33c8</t>
+          <t>08a1034f-2303-490d-93f9-e826b8a3d7a6</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -14671,34 +14671,34 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-10-21T13:13:41+00:00</t>
+          <t>2026-10-20T14:09:01+00:00</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>f59b2607-a6e7-46ba-b490-4d518c4f33c8</t>
+          <t>08a1034f-2303-490d-93f9-e826b8a3d7a6</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -14713,29 +14713,29 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-10-20T15:00:43+00:00</t>
+          <t>2026-10-17T07:52:06+00:00</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>f59b2607-a6e7-46ba-b490-4d518c4f33c8</t>
+          <t>08a1034f-2303-490d-93f9-e826b8a3d7a6</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -14745,34 +14745,34 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-10-16T21:05:16+00:00</t>
+          <t>2026-10-16T09:23:37+00:00</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>a11eb8b3-501d-4ee8-9054-39ff57433e6b</t>
+          <t>daf518c0-89db-4a9e-8a5b-6bb1b858a1a8</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -14792,24 +14792,24 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-10-20T05:48:13+00:00</t>
+          <t>2026-10-18T19:57:22+00:00</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>a11eb8b3-501d-4ee8-9054-39ff57433e6b</t>
+          <t>daf518c0-89db-4a9e-8a5b-6bb1b858a1a8</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14819,17 +14819,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -14839,14 +14839,14 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-10-20T12:20:16+00:00</t>
+          <t>2026-10-18T13:29:45+00:00</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>a11eb8b3-501d-4ee8-9054-39ff57433e6b</t>
+          <t>daf518c0-89db-4a9e-8a5b-6bb1b858a1a8</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -14871,19 +14871,19 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-10-17T08:25:08+00:00</t>
+          <t>2026-10-21T00:38:47+00:00</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5571a61f-fbab-4aea-a84a-3aabbf728603</t>
+          <t>902ab14b-6ea2-4fe0-818f-c8a236ff9da7</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -14913,14 +14913,14 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-10-17T04:39:28+00:00</t>
+          <t>2026-10-21T06:10:07+00:00</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5571a61f-fbab-4aea-a84a-3aabbf728603</t>
+          <t>902ab14b-6ea2-4fe0-818f-c8a236ff9da7</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -14950,14 +14950,14 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-10-17T21:37:40+00:00</t>
+          <t>2026-10-16T14:07:44+00:00</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5571a61f-fbab-4aea-a84a-3aabbf728603</t>
+          <t>902ab14b-6ea2-4fe0-818f-c8a236ff9da7</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14972,29 +14972,29 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-10-18T18:19:11+00:00</t>
+          <t>2026-10-20T18:49:19+00:00</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>f04f4893-fd8f-4a95-a551-29d2746862cf</t>
+          <t>98b02370-411a-496d-aac7-cd92709d3525</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -15004,12 +15004,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -15024,14 +15024,14 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-10-17T01:24:18+00:00</t>
+          <t>2026-10-17T02:55:20+00:00</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>f04f4893-fd8f-4a95-a551-29d2746862cf</t>
+          <t>98b02370-411a-496d-aac7-cd92709d3525</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -15046,12 +15046,12 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -15061,14 +15061,14 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-10-20T09:39:34+00:00</t>
+          <t>2026-10-17T12:13:51+00:00</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>f04f4893-fd8f-4a95-a551-29d2746862cf</t>
+          <t>98b02370-411a-496d-aac7-cd92709d3525</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -15078,34 +15078,34 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-10-17T11:02:58+00:00</t>
+          <t>2026-10-17T16:03:54+00:00</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>b8a565c9-994e-4cf6-b911-3421aef9b97c</t>
+          <t>a7406ce0-ccae-4cbe-8ca4-447f377ca12f</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -15120,29 +15120,29 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-10-21T00:48:24+00:00</t>
+          <t>2026-10-16T16:32:32+00:00</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>b8a565c9-994e-4cf6-b911-3421aef9b97c</t>
+          <t>a7406ce0-ccae-4cbe-8ca4-447f377ca12f</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -15152,34 +15152,34 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Discount</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-10-17T04:10:36+00:00</t>
+          <t>2026-10-18T07:08:33+00:00</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>b8a565c9-994e-4cf6-b911-3421aef9b97c</t>
+          <t>a7406ce0-ccae-4cbe-8ca4-447f377ca12f</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -15189,12 +15189,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -15209,14 +15209,14 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-10-16T18:04:57+00:00</t>
+          <t>2026-10-18T16:10:05+00:00</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>e06d0613-79bd-40e2-8ef0-89ea67ae0a89</t>
+          <t>7fc26476-940c-4b2b-9eb3-f601a01ae572</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -15226,12 +15226,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>No Promotion</t>
+          <t>Cashback</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -15246,14 +15246,14 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-10-18T16:38:10+00:00</t>
+          <t>2026-10-21T14:05:47+00:00</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>e06d0613-79bd-40e2-8ef0-89ea67ae0a89</t>
+          <t>7fc26476-940c-4b2b-9eb3-f601a01ae572</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Cashback</t>
+          <t>No Promotion</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -15273,24 +15273,24 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-10-18T10:47:50+00:00</t>
+          <t>2026-10-20T22:15:32+00:00</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>e06d0613-79bd-40e2-8ef0-89ea67ae0a89</t>
+          <t>7fc26476-940c-4b2b-9eb3-f601a01ae572</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -15305,12 +15305,12 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -15319,672 +15319,6 @@
         </is>
       </c>
       <c r="G223" t="inlineStr">
-        <is>
-          <t>2026-10-17T10:50:50+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>08a1034f-2303-490d-93f9-e826b8a3d7a6</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>No Promotion</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>2026-10-20T14:09:01+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>08a1034f-2303-490d-93f9-e826b8a3d7a6</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>2026-10-17T07:52:06+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>08a1034f-2303-490d-93f9-e826b8a3d7a6</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Cashback</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>2026-10-16T09:23:37+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>daf518c0-89db-4a9e-8a5b-6bb1b858a1a8</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>2026-10-18T19:57:22+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>daf518c0-89db-4a9e-8a5b-6bb1b858a1a8</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>No Promotion</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>2026-10-18T13:29:45+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>daf518c0-89db-4a9e-8a5b-6bb1b858a1a8</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Cashback</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>2026-10-21T00:38:47+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>902ab14b-6ea2-4fe0-818f-c8a236ff9da7</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>2026-10-21T06:10:07+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>902ab14b-6ea2-4fe0-818f-c8a236ff9da7</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Cashback</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>2026-10-16T14:07:44+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>902ab14b-6ea2-4fe0-818f-c8a236ff9da7</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>No Promotion</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>2026-10-20T18:49:19+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>98b02370-411a-496d-aac7-cd92709d3525</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>2026-10-17T02:55:20+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>98b02370-411a-496d-aac7-cd92709d3525</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>No Promotion</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>2026-10-17T12:13:51+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>98b02370-411a-496d-aac7-cd92709d3525</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Cashback</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>2026-10-17T16:03:54+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>a7406ce0-ccae-4cbe-8ca4-447f377ca12f</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Cashback</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>2026-10-16T16:32:32+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>a7406ce0-ccae-4cbe-8ca4-447f377ca12f</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>2026-10-18T07:08:33+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>a7406ce0-ccae-4cbe-8ca4-447f377ca12f</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>No Promotion</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>2026-10-18T16:10:05+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>7fc26476-940c-4b2b-9eb3-f601a01ae572</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Cashback</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>2026-10-21T14:05:47+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>7fc26476-940c-4b2b-9eb3-f601a01ae572</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>No Promotion</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>2026-10-20T22:15:32+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>7fc26476-940c-4b2b-9eb3-f601a01ae572</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
         <is>
           <t>2026-10-20T05:09:10+00:00</t>
         </is>
